--- a/数据库/合同列表/昂氏公司合同模板2025.1_HB20260328-001.xlsx
+++ b/数据库/合同列表/昂氏公司合同模板2025.1_HB20260328-001.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t>绍兴宏邦电子科技有限公司  采购合同</t>
   </si>
@@ -31,7 +31,7 @@
     <t>制表日期：</t>
   </si>
   <si>
-    <t>2026/3/28</t>
+    <t>****</t>
   </si>
   <si>
     <t>买方：</t>
@@ -103,55 +103,19 @@
     <t>衣服</t>
   </si>
   <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>d1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e1 </t>
-  </si>
-  <si>
-    <t>个</t>
+    <t>件</t>
   </si>
   <si>
     <t>裤子</t>
   </si>
   <si>
-    <t>d2</t>
-  </si>
-  <si>
-    <t>e2</t>
-  </si>
-  <si>
     <t>条</t>
   </si>
   <si>
     <t>鞋子</t>
   </si>
   <si>
-    <t>c3</t>
-  </si>
-  <si>
-    <t>d43</t>
-  </si>
-  <si>
-    <t>e3</t>
-  </si>
-  <si>
     <t>双</t>
-  </si>
-  <si>
-    <t>手套</t>
-  </si>
-  <si>
-    <t>c4</t>
-  </si>
-  <si>
-    <t>d4</t>
-  </si>
-  <si>
-    <t>e4</t>
   </si>
   <si>
     <t>合计</t>
@@ -819,23 +783,17 @@
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="12">
-        <v>50</v>
-      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12">
+        <v>18</v>
+      </c>
       <c r="J9" s="12">
         <f>$G9*$I9</f>
       </c>
@@ -847,25 +805,19 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="12">
-        <v>100</v>
-      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12">
+        <v>78</v>
+      </c>
       <c r="J10" s="12">
         <f>$G10*$I10</f>
       </c>
@@ -877,25 +829,19 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="12">
-        <v>80</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="I11" s="12">
+        <v>12</v>
+      </c>
       <c r="J11" s="12">
         <f>$G11*$I11</f>
       </c>
@@ -907,25 +853,19 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="12">
-        <v>300</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G12" s="12"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="I12" s="12">
+        <v>22</v>
+      </c>
       <c r="J12" s="12">
         <f>$G12*$I12</f>
       </c>
@@ -934,7 +874,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -952,7 +892,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -968,7 +908,7 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -984,7 +924,7 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1000,7 +940,7 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1016,7 +956,7 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -1032,7 +972,7 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -1048,7 +988,7 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -1064,7 +1004,7 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -1094,7 +1034,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1103,7 +1043,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1112,7 +1052,7 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1121,7 +1061,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -1130,7 +1070,7 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1139,7 +1079,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
